--- a/faculty_input.xlsx
+++ b/faculty_input.xlsx
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dr Shashikant Gupta</t>
+          <t>Dr. Shashikant Gupta</t>
         </is>
       </c>
     </row>
